--- a/tabelas/2021.xlsx
+++ b/tabelas/2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapilotodois-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB3819B-19ED-4B72-9FCB-12E132C7EDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48A58036-02E4-42FC-863A-025D49B97FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="213">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -655,6 +655,15 @@
   </si>
   <si>
     <t>08.779.141.0024.001</t>
+  </si>
+  <si>
+    <t>08.777.141.0012.002</t>
+  </si>
+  <si>
+    <t>08.778.141.0030.003</t>
+  </si>
+  <si>
+    <t>08.779.141.0040.002</t>
   </si>
 </sst>
 </file>
@@ -704,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -714,7 +723,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1029,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEC8DEA-D1AE-4B91-B66D-48CA0A2026FB}">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1112,7 +1120,7 @@
       <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1144,55 +1152,58 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>35</v>
+      <c r="A4" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2">
         <v>2021</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>35.74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2">
         <v>2021</v>
@@ -1200,6 +1211,9 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="J5" t="s">
         <v>29</v>
       </c>
@@ -1208,11 +1222,8 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
+      <c r="A6" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>44</v>
@@ -1230,21 +1241,18 @@
         <v>2021</v>
       </c>
       <c r="H6" s="2">
-        <v>35</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>42</v>
+      <c r="A7" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>41</v>
@@ -1265,21 +1273,21 @@
         <v>2021</v>
       </c>
       <c r="H7" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
+      <c r="A8" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>41</v>
@@ -1300,13 +1308,13 @@
         <v>2021</v>
       </c>
       <c r="H8" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
         <v>30</v>
@@ -1314,39 +1322,42 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2">
         <v>2021</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="J9" t="s">
         <v>29</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
+      <c r="A10" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>44</v>
@@ -1364,21 +1375,18 @@
         <v>2021</v>
       </c>
       <c r="H10" s="2">
-        <v>60</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J10" t="s">
         <v>29</v>
       </c>
       <c r="K10" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>46</v>
+      <c r="A11" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>45</v>
@@ -1399,7 +1407,7 @@
         <v>2021</v>
       </c>
       <c r="H11" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>61</v>
@@ -1413,7 +1421,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>45</v>
@@ -1434,7 +1442,7 @@
         <v>2021</v>
       </c>
       <c r="H12" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>61</v>
@@ -1448,7 +1456,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>45</v>
@@ -1469,7 +1477,7 @@
         <v>2021</v>
       </c>
       <c r="H13" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>61</v>
@@ -1483,7 +1491,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>45</v>
@@ -1504,7 +1512,7 @@
         <v>2021</v>
       </c>
       <c r="H14" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>61</v>
@@ -1513,12 +1521,12 @@
         <v>29</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>50</v>
+      <c r="A15" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>45</v>
@@ -1539,21 +1547,21 @@
         <v>2021</v>
       </c>
       <c r="H15" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>51</v>
+      <c r="A16" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>45</v>
@@ -1574,21 +1582,21 @@
         <v>2021</v>
       </c>
       <c r="H16" s="2">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="J16" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>52</v>
+      <c r="A17" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>45</v>
@@ -1609,7 +1617,7 @@
         <v>2021</v>
       </c>
       <c r="H17" s="2">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>64</v>
@@ -1623,39 +1631,42 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="2">
         <v>2021</v>
       </c>
       <c r="H18" s="2">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="J18" t="s">
         <v>29</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>44</v>
@@ -1673,24 +1684,21 @@
         <v>2021</v>
       </c>
       <c r="H19" s="2">
-        <v>70</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J19" t="s">
         <v>29</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>44</v>
@@ -1711,7 +1719,7 @@
         <v>70</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
         <v>29</v>
@@ -1722,10 +1730,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>44</v>
@@ -1746,7 +1754,7 @@
         <v>70</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J21" t="s">
         <v>29</v>
@@ -1757,10 +1765,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>44</v>
@@ -1781,7 +1789,7 @@
         <v>70</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J22" t="s">
         <v>29</v>
@@ -1792,10 +1800,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>44</v>
@@ -1816,7 +1824,7 @@
         <v>70</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J23" t="s">
         <v>29</v>
@@ -1827,10 +1835,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>44</v>
@@ -1851,7 +1859,7 @@
         <v>70</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J24" t="s">
         <v>29</v>
@@ -1862,10 +1870,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>44</v>
@@ -1886,7 +1894,7 @@
         <v>70</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s">
         <v>29</v>
@@ -1897,10 +1905,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>44</v>
@@ -1921,7 +1929,7 @@
         <v>70</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s">
         <v>29</v>
@@ -1932,10 +1940,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>44</v>
@@ -1956,7 +1964,7 @@
         <v>70</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s">
         <v>29</v>
@@ -1967,10 +1975,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>44</v>
@@ -1991,7 +1999,7 @@
         <v>70</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s">
         <v>29</v>
@@ -2002,10 +2010,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>44</v>
@@ -2026,7 +2034,7 @@
         <v>70</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
         <v>29</v>
@@ -2037,10 +2045,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>44</v>
@@ -2061,7 +2069,7 @@
         <v>70</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s">
         <v>29</v>
@@ -2072,10 +2080,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>44</v>
@@ -2096,7 +2104,7 @@
         <v>70</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s">
         <v>29</v>
@@ -2107,10 +2115,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>44</v>
@@ -2131,7 +2139,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s">
         <v>29</v>
@@ -2142,10 +2150,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>44</v>
@@ -2166,7 +2174,7 @@
         <v>70</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s">
         <v>29</v>
@@ -2177,39 +2185,42 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G34" s="2">
         <v>2021</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="J34" t="s">
         <v>29</v>
       </c>
       <c r="K34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>97</v>
@@ -2227,53 +2238,53 @@
         <v>2021</v>
       </c>
       <c r="H35" s="2">
-        <v>130</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J35" t="s">
         <v>29</v>
       </c>
       <c r="K35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="2">
         <v>2021</v>
       </c>
       <c r="H36" s="2">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>97</v>
@@ -2291,53 +2302,53 @@
         <v>2021</v>
       </c>
       <c r="H37" s="2">
-        <v>70</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="J37" t="s">
         <v>65</v>
       </c>
       <c r="K37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" s="2">
         <v>2021</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="J38" t="s">
         <v>65</v>
       </c>
       <c r="K38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>97</v>
@@ -2355,53 +2366,53 @@
         <v>2021</v>
       </c>
       <c r="H39" s="2">
-        <v>205</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
         <v>65</v>
       </c>
       <c r="K39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" s="2">
         <v>2021</v>
       </c>
       <c r="H40" s="2">
-        <v>0</v>
+        <v>205</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="J40" t="s">
         <v>65</v>
       </c>
       <c r="K40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>97</v>
@@ -2419,42 +2430,45 @@
         <v>2021</v>
       </c>
       <c r="H41" s="2">
-        <v>215</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J41" t="s">
         <v>65</v>
       </c>
       <c r="K41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="2">
         <v>2021</v>
       </c>
       <c r="H42" s="2">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="J42" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="K42" t="s">
         <v>30</v>
@@ -2462,10 +2476,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>97</v>
@@ -2483,10 +2494,7 @@
         <v>2021</v>
       </c>
       <c r="H43" s="2">
-        <v>225</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J43" t="s">
         <v>113</v>
@@ -2497,39 +2505,42 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G44" s="2">
         <v>2021</v>
       </c>
       <c r="H44" s="2">
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="J44" t="s">
         <v>113</v>
       </c>
       <c r="K44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>97</v>
@@ -2547,53 +2558,53 @@
         <v>2021</v>
       </c>
       <c r="H45" s="2">
-        <v>235</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J45" t="s">
         <v>113</v>
       </c>
       <c r="K45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" s="2">
         <v>2021</v>
       </c>
       <c r="H46" s="2">
-        <v>0</v>
+        <v>235</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="J46" t="s">
         <v>113</v>
       </c>
       <c r="K46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>97</v>
@@ -2611,53 +2622,53 @@
         <v>2021</v>
       </c>
       <c r="H47" s="2">
-        <v>245</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="J47" t="s">
         <v>113</v>
       </c>
       <c r="K47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48" s="2">
         <v>2021</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>245</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="J48" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="K48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>97</v>
@@ -2675,53 +2686,53 @@
         <v>2021</v>
       </c>
       <c r="H49" s="2">
-        <v>255</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J49" t="s">
         <v>65</v>
       </c>
       <c r="K49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50" s="2">
         <v>2021</v>
       </c>
       <c r="H50" s="2">
-        <v>0</v>
+        <v>255</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="J50" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>97</v>
@@ -2739,53 +2750,53 @@
         <v>2021</v>
       </c>
       <c r="H51" s="2">
-        <v>265</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J51" t="s">
         <v>29</v>
       </c>
       <c r="K51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2">
         <v>2021</v>
       </c>
       <c r="H52" s="2">
-        <v>0</v>
+        <v>265</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J52" t="s">
         <v>29</v>
       </c>
       <c r="K52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>97</v>
@@ -2803,53 +2814,53 @@
         <v>2021</v>
       </c>
       <c r="H53" s="2">
-        <v>275</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J53" t="s">
         <v>29</v>
       </c>
       <c r="K53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G54" s="2">
         <v>2021</v>
       </c>
       <c r="H54" s="2">
-        <v>0</v>
+        <v>275</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J54" t="s">
         <v>29</v>
       </c>
       <c r="K54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>97</v>
@@ -2867,53 +2878,53 @@
         <v>2021</v>
       </c>
       <c r="H55" s="2">
-        <v>285</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J55" t="s">
         <v>29</v>
       </c>
       <c r="K55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="G56" s="2">
         <v>2021</v>
       </c>
       <c r="H56" s="2">
-        <v>0</v>
+        <v>285</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J56" t="s">
         <v>29</v>
       </c>
       <c r="K56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>97</v>
@@ -2931,53 +2942,53 @@
         <v>2021</v>
       </c>
       <c r="H57" s="2">
-        <v>80</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J57" t="s">
         <v>29</v>
       </c>
       <c r="K57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G58" s="2">
         <v>2021</v>
       </c>
       <c r="H58" s="2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J58" t="s">
         <v>29</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>97</v>
@@ -2995,53 +3006,53 @@
         <v>2021</v>
       </c>
       <c r="H59" s="2">
-        <v>81</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J59" t="s">
         <v>29</v>
       </c>
       <c r="K59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G60" s="2">
         <v>2021</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J60" t="s">
         <v>29</v>
       </c>
       <c r="K60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>97</v>
@@ -3059,53 +3070,53 @@
         <v>2021</v>
       </c>
       <c r="H61" s="2">
-        <v>95</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J61" t="s">
         <v>29</v>
       </c>
       <c r="K61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G62" s="2">
         <v>2021</v>
       </c>
       <c r="H62" s="2">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J62" t="s">
         <v>29</v>
       </c>
       <c r="K62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>97</v>
@@ -3123,53 +3134,53 @@
         <v>2021</v>
       </c>
       <c r="H63" s="2">
-        <v>90</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J63" t="s">
         <v>29</v>
       </c>
       <c r="K63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G64" s="2">
         <v>2021</v>
       </c>
       <c r="H64" s="2">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J64" t="s">
         <v>29</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>97</v>
@@ -3187,53 +3198,53 @@
         <v>2021</v>
       </c>
       <c r="H65" s="2">
-        <v>100</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J65" t="s">
         <v>29</v>
       </c>
       <c r="K65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G66" s="2">
         <v>2021</v>
       </c>
       <c r="H66" s="2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J66" t="s">
         <v>29</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>97</v>
@@ -3251,53 +3262,53 @@
         <v>2021</v>
       </c>
       <c r="H67" s="2">
-        <v>110</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J67" t="s">
         <v>29</v>
       </c>
       <c r="K67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="G68" s="2">
         <v>2021</v>
       </c>
       <c r="H68" s="2">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J68" t="s">
         <v>29</v>
       </c>
       <c r="K68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>97</v>
@@ -3315,53 +3326,53 @@
         <v>2021</v>
       </c>
       <c r="H69" s="2">
-        <v>75</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J69" t="s">
         <v>29</v>
       </c>
       <c r="K69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G70" s="2">
         <v>2021</v>
       </c>
       <c r="H70" s="2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J70" t="s">
         <v>29</v>
       </c>
       <c r="K70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>97</v>
@@ -3379,53 +3390,53 @@
         <v>2021</v>
       </c>
       <c r="H71" s="2">
-        <v>75</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J71" t="s">
         <v>29</v>
       </c>
       <c r="K71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>124</v>
+        <v>156</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G72" s="2">
         <v>2021</v>
       </c>
       <c r="H72" s="2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J72" t="s">
         <v>29</v>
       </c>
       <c r="K72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>97</v>
@@ -3443,53 +3454,53 @@
         <v>2021</v>
       </c>
       <c r="H73" s="2">
-        <v>85</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J73" t="s">
         <v>29</v>
       </c>
       <c r="K73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G74" s="2">
         <v>2021</v>
       </c>
       <c r="H74" s="2">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J74" t="s">
         <v>29</v>
       </c>
       <c r="K74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>97</v>
@@ -3507,53 +3518,53 @@
         <v>2021</v>
       </c>
       <c r="H75" s="2">
-        <v>90</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J75" t="s">
         <v>29</v>
       </c>
       <c r="K75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="G76" s="2">
         <v>2021</v>
       </c>
       <c r="H76" s="2">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J76" t="s">
         <v>29</v>
       </c>
       <c r="K76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>186</v>
@@ -3571,65 +3582,65 @@
         <v>2021</v>
       </c>
       <c r="H77" s="2">
-        <v>95</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J77" t="s">
         <v>29</v>
       </c>
       <c r="K77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>158</v>
+        <v>185</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" s="2">
         <v>2021</v>
       </c>
       <c r="H78" s="2">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J78" t="s">
         <v>29</v>
       </c>
       <c r="K78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" s="2">
         <v>2021</v>
@@ -3637,6 +3648,9 @@
       <c r="H79" s="2">
         <v>0</v>
       </c>
+      <c r="I79" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="J79" t="s">
         <v>29</v>
       </c>
@@ -3646,16 +3660,13 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>6</v>
@@ -3667,21 +3678,18 @@
         <v>2021</v>
       </c>
       <c r="H80" s="2">
-        <v>120</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J80" t="s">
         <v>29</v>
       </c>
       <c r="K80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>160</v>
@@ -3702,10 +3710,10 @@
         <v>2021</v>
       </c>
       <c r="H81" s="2">
-        <v>54.5</v>
+        <v>120</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J81" t="s">
         <v>29</v>
@@ -3716,60 +3724,66 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G82" s="2">
         <v>2021</v>
       </c>
       <c r="H82" s="2">
-        <v>0</v>
+        <v>54.5</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="J82" t="s">
         <v>29</v>
       </c>
       <c r="K82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>163</v>
+      <c r="A83" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G83" s="2">
         <v>2021</v>
       </c>
       <c r="H83" s="2">
-        <v>97</v>
+        <v>54.5</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="J83" t="s">
         <v>29</v>
@@ -3780,10 +3794,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>186</v>
@@ -3801,21 +3812,18 @@
         <v>2021</v>
       </c>
       <c r="H84" s="2">
-        <v>123.78</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J84" t="s">
         <v>29</v>
       </c>
       <c r="K84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>163</v>
@@ -3836,7 +3844,7 @@
         <v>2021</v>
       </c>
       <c r="H85" s="2">
-        <v>150.41999999999999</v>
+        <v>97</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>61</v>
@@ -3850,63 +3858,69 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G86" s="2">
         <v>2021</v>
       </c>
       <c r="H86" s="2">
-        <v>420</v>
+        <v>123.78</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J86" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="K86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>186</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G87" s="2">
         <v>2021</v>
       </c>
       <c r="H87" s="2">
-        <v>425</v>
+        <v>150.41999999999999</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J87" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="K87" t="s">
         <v>30</v>
@@ -3914,10 +3928,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>186</v>
@@ -3935,77 +3946,80 @@
         <v>2021</v>
       </c>
       <c r="H88" s="2">
-        <v>430</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>59</v>
+        <v>420</v>
       </c>
       <c r="J88" t="s">
         <v>65</v>
       </c>
       <c r="K88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G89" s="2">
         <v>2021</v>
       </c>
       <c r="H89" s="2">
-        <v>0</v>
+        <v>425</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="J89" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G90" s="2">
         <v>2021</v>
       </c>
       <c r="H90" s="2">
-        <v>505</v>
+        <v>430</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J90" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="K90" t="s">
         <v>30</v>
@@ -4013,19 +4027,19 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G91" s="2">
         <v>2021</v>
@@ -4042,28 +4056,28 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" s="2">
         <v>2021</v>
       </c>
       <c r="H92" s="2">
-        <v>320</v>
+        <v>505</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>61</v>
@@ -4077,19 +4091,19 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" s="2">
         <v>2021</v>
@@ -4106,28 +4120,28 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G94" s="2">
         <v>2021</v>
       </c>
       <c r="H94" s="2">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>61</v>
@@ -4141,19 +4155,19 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G95" s="2">
         <v>2021</v>
@@ -4170,28 +4184,28 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G96" s="2">
         <v>2021</v>
       </c>
       <c r="H96" s="2">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>61</v>
@@ -4205,19 +4219,19 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G97" s="2">
         <v>2021</v>
@@ -4234,28 +4248,28 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G98" s="2">
         <v>2021</v>
       </c>
       <c r="H98" s="2">
-        <v>360</v>
+        <v>220</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>61</v>
@@ -4269,19 +4283,19 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G99" s="2">
         <v>2021</v>
@@ -4298,28 +4312,28 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G100" s="2">
         <v>2021</v>
       </c>
       <c r="H100" s="2">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>61</v>
@@ -4333,19 +4347,19 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G101" s="2">
         <v>2021</v>
@@ -4362,28 +4376,28 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G102" s="2">
         <v>2021</v>
       </c>
       <c r="H102" s="2">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>61</v>
@@ -4397,19 +4411,19 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G103" s="2">
         <v>2021</v>
@@ -4426,28 +4440,28 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>187</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G104" s="2">
         <v>2021</v>
       </c>
       <c r="H104" s="2">
-        <v>575</v>
+        <v>167</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>61</v>
@@ -4461,19 +4475,19 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G105" s="2">
         <v>2021</v>
@@ -4490,28 +4504,28 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G106" s="2">
         <v>2021</v>
       </c>
       <c r="H106" s="2">
-        <v>100.23</v>
+        <v>575</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>61</v>
@@ -4525,19 +4539,19 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G107" s="2">
         <v>2021</v>
@@ -4554,28 +4568,28 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G108" s="2">
         <v>2021</v>
       </c>
       <c r="H108" s="2">
-        <v>95.46</v>
+        <v>100.23</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>61</v>
@@ -4584,24 +4598,24 @@
         <v>29</v>
       </c>
       <c r="K108" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G109" s="2">
         <v>2021</v>
@@ -4618,28 +4632,28 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G110" s="2">
         <v>2021</v>
       </c>
       <c r="H110" s="2">
-        <v>155.78</v>
+        <v>95.46</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>61</v>
@@ -4648,24 +4662,24 @@
         <v>29</v>
       </c>
       <c r="K110" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G111" s="2">
         <v>2021</v>
@@ -4682,28 +4696,28 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G112" s="2">
         <v>2021</v>
       </c>
       <c r="H112" s="2">
-        <v>236.65</v>
+        <v>155.78</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>61</v>
@@ -4717,19 +4731,19 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G113" s="2">
         <v>2021</v>
@@ -4746,28 +4760,28 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G114" s="2">
         <v>2021</v>
       </c>
       <c r="H114" s="2">
-        <v>74.25</v>
+        <v>236.65</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>61</v>
@@ -4776,318 +4790,315 @@
         <v>29</v>
       </c>
       <c r="K114" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>197</v>
+      <c r="A115" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G115" s="2">
         <v>2021</v>
       </c>
       <c r="H115" s="2">
-        <v>0</v>
+        <v>27.84</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="J115" t="s">
         <v>29</v>
       </c>
       <c r="K115" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G116" s="2">
         <v>2021</v>
       </c>
       <c r="H116" s="2">
-        <v>89.36</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J116" t="s">
         <v>29</v>
       </c>
       <c r="K116" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G117" s="2">
         <v>2021</v>
       </c>
       <c r="H117" s="2">
-        <v>0</v>
+        <v>74.25</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J117" t="s">
         <v>29</v>
       </c>
       <c r="K117" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F118" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G118" s="2">
         <v>2021</v>
       </c>
       <c r="H118" s="2">
-        <v>247.87</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J118" t="s">
         <v>29</v>
       </c>
       <c r="K118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F119" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="G119" s="2">
         <v>2021</v>
       </c>
       <c r="H119" s="2">
-        <v>0</v>
+        <v>89.36</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J119" t="s">
         <v>29</v>
       </c>
       <c r="K119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G120" s="2">
         <v>2021</v>
       </c>
       <c r="H120" s="2">
-        <v>100</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J120" t="s">
         <v>29</v>
       </c>
       <c r="K120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G121" s="2">
         <v>2021</v>
       </c>
       <c r="H121" s="2">
-        <v>0</v>
+        <v>247.87</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="J121" t="s">
         <v>29</v>
       </c>
       <c r="K121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>204</v>
+      <c r="A122" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G122" s="2">
         <v>2021</v>
       </c>
       <c r="H122" s="2">
-        <v>120.75</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J122" t="s">
         <v>29</v>
       </c>
       <c r="K122" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G123" s="2">
         <v>2021</v>
       </c>
       <c r="H123" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J123" t="s">
         <v>29</v>
       </c>
       <c r="K123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G124" s="2">
         <v>2021</v>
@@ -5095,9 +5106,6 @@
       <c r="H124" s="2">
         <v>0</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="J124" t="s">
         <v>29</v>
       </c>
@@ -5106,58 +5114,58 @@
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>207</v>
+      <c r="A125" s="4" t="s">
+        <v>204</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G125" s="2">
         <v>2021</v>
       </c>
       <c r="H125" s="2">
-        <v>0</v>
+        <v>120.75</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J125" t="s">
         <v>29</v>
       </c>
       <c r="K125" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G126" s="2">
         <v>2021</v>
@@ -5174,6 +5182,86 @@
       <c r="K126" t="s">
         <v>31</v>
       </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="2">
+        <v>2021</v>
+      </c>
+      <c r="H127" s="2">
+        <v>0</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J127" t="s">
+        <v>29</v>
+      </c>
+      <c r="K127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" s="2">
+        <v>2021</v>
+      </c>
+      <c r="H128" s="2">
+        <v>0</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J128" t="s">
+        <v>29</v>
+      </c>
+      <c r="K128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
